--- a/xplate-web/backend/reports/daily_rules/xplate_rule_report_349716df-a9f4-4337-b4c1-d2dea75b487c_2026-06-27.xlsx
+++ b/xplate-web/backend/reports/daily_rules/xplate_rule_report_349716df-a9f4-4337-b4c1-d2dea75b487c_2026-06-27.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>{"cities": ["Ras Al Khaimah", "Sharjah"], "city": "Ras Al Khaimah", "number_format": "xxyxx (5 Digits)", "number_formats": ["xxyxx_5", "xyxyx_5", "xyyyx_5", "xyyyy_5", "xxx??_5", "xxyyy_5", "xxxyy_5", "xxxyx_5", "xyxxx_5", "xxxxy_5", "xyxxy_5", "xxxxx_5", "xyyx_4", "x??x_4", "xyxy_4", "xxxy_4", "xyyy_4", "xyxx_4", "xxyx_4", "xxyy_4", "xxxx_4"], "search_mode": "Send all new plates", "send_all_new_plates": true}</t>
+          <t>{"cities": ["Ras Al Khaimah", "Sharjah"], "city": "Ras Al Khaimah", "number_format": "xxyxx (5 Digits)", "number_formats": ["xxyxx_5", "xyxyx_5", "xyyyx_5", "xyyyy_5", "xxx??_5", "xxyyy_5", "xxxyy_5", "xxxyx_5", "xyxxx_5", "xxxxy_5", "xyxxy_5", "xxxxx_5", "xyyx_4", "x??x_4", "xyxy_4", "xxxy_4", "xyyy_4", "xyxx_4", "xxyx_4", "xxyy_4", "xxxx_4", "xxx_3", "xxy_3", "xyy_3", "xyx_3", "xyz_3"], "search_mode": "Send all new plates", "send_all_new_plates": true}</t>
         </is>
       </c>
     </row>
